--- a/vix_pkg/data/all_cmfs_oos_predictions.xlsx
+++ b/vix_pkg/data/all_cmfs_oos_predictions.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O503"/>
+  <dimension ref="A1:O522"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25107,6 +25107,937 @@
         <v>586.08</v>
       </c>
     </row>
+    <row r="504">
+      <c r="A504" s="2" t="n">
+        <v>45659</v>
+      </c>
+      <c r="B504" t="n">
+        <v>-0.05963270401175071</v>
+      </c>
+      <c r="C504" t="n">
+        <v>-0.07077131620466894</v>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>Fold4</t>
+        </is>
+      </c>
+      <c r="E504" t="n">
+        <v>-0.04120498139699766</v>
+      </c>
+      <c r="F504" t="n">
+        <v>-0.04625966661717171</v>
+      </c>
+      <c r="G504" t="n">
+        <v>-0.03080073658519225</v>
+      </c>
+      <c r="H504" t="n">
+        <v>-0.032478035736308</v>
+      </c>
+      <c r="I504" t="n">
+        <v>-0.02396727510074366</v>
+      </c>
+      <c r="J504" t="n">
+        <v>-0.02457404582953592</v>
+      </c>
+      <c r="K504" t="n">
+        <v>-0.02149615328543419</v>
+      </c>
+      <c r="L504" t="n">
+        <v>-0.0221098540859956</v>
+      </c>
+      <c r="M504" t="n">
+        <v>-0.0199011223453561</v>
+      </c>
+      <c r="N504" t="n">
+        <v>-0.02016061010946565</v>
+      </c>
+      <c r="O504" t="n">
+        <v>584.64</v>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" s="2" t="n">
+        <v>45660</v>
+      </c>
+      <c r="B505" t="n">
+        <v>-0.005115470869560317</v>
+      </c>
+      <c r="C505" t="n">
+        <v>0.02053964098550443</v>
+      </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>Fold4</t>
+        </is>
+      </c>
+      <c r="E505" t="n">
+        <v>-0.003410789919273839</v>
+      </c>
+      <c r="F505" t="n">
+        <v>0.02010939519160861</v>
+      </c>
+      <c r="G505" t="n">
+        <v>-0.004471430311727944</v>
+      </c>
+      <c r="H505" t="n">
+        <v>0.01779946174587799</v>
+      </c>
+      <c r="I505" t="n">
+        <v>-0.007982616024716343</v>
+      </c>
+      <c r="J505" t="n">
+        <v>0.01326945864513487</v>
+      </c>
+      <c r="K505" t="n">
+        <v>-0.01086857617633981</v>
+      </c>
+      <c r="L505" t="n">
+        <v>0.01005177723768796</v>
+      </c>
+      <c r="M505" t="n">
+        <v>-0.0127913299572494</v>
+      </c>
+      <c r="N505" t="n">
+        <v>0.007568450002766037</v>
+      </c>
+      <c r="O505" t="n">
+        <v>591.95</v>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" s="2" t="n">
+        <v>45663</v>
+      </c>
+      <c r="B506" t="n">
+        <v>0.06150348777915386</v>
+      </c>
+      <c r="C506" t="n">
+        <v>0.06119394761843744</v>
+      </c>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>Fold4</t>
+        </is>
+      </c>
+      <c r="E506" t="n">
+        <v>0.04441152990221092</v>
+      </c>
+      <c r="F506" t="n">
+        <v>0.03944807455579738</v>
+      </c>
+      <c r="G506" t="n">
+        <v>0.03591242205442289</v>
+      </c>
+      <c r="H506" t="n">
+        <v>0.02793896680245652</v>
+      </c>
+      <c r="I506" t="n">
+        <v>0.03075336354522062</v>
+      </c>
+      <c r="J506" t="n">
+        <v>0.02192880729219226</v>
+      </c>
+      <c r="K506" t="n">
+        <v>0.02861477078367699</v>
+      </c>
+      <c r="L506" t="n">
+        <v>0.01959926715199156</v>
+      </c>
+      <c r="M506" t="n">
+        <v>0.02708876189024303</v>
+      </c>
+      <c r="N506" t="n">
+        <v>0.01779923112736257</v>
+      </c>
+      <c r="O506" t="n">
+        <v>595.36</v>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" s="2" t="n">
+        <v>45664</v>
+      </c>
+      <c r="B507" t="n">
+        <v>-0.007321246855279697</v>
+      </c>
+      <c r="C507" t="n">
+        <v>-0.02087175209811762</v>
+      </c>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>Fold4</t>
+        </is>
+      </c>
+      <c r="E507" t="n">
+        <v>-0.003410179269915551</v>
+      </c>
+      <c r="F507" t="n">
+        <v>-0.01425871657086776</v>
+      </c>
+      <c r="G507" t="n">
+        <v>0.001050096958878447</v>
+      </c>
+      <c r="H507" t="n">
+        <v>-0.008808139397386085</v>
+      </c>
+      <c r="I507" t="n">
+        <v>0.003573629104328146</v>
+      </c>
+      <c r="J507" t="n">
+        <v>-0.006243245041743341</v>
+      </c>
+      <c r="K507" t="n">
+        <v>0.003784029039887061</v>
+      </c>
+      <c r="L507" t="n">
+        <v>-0.006696953957515802</v>
+      </c>
+      <c r="M507" t="n">
+        <v>0.003664000318287001</v>
+      </c>
+      <c r="N507" t="n">
+        <v>-0.007068574781900911</v>
+      </c>
+      <c r="O507" t="n">
+        <v>588.63</v>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" s="2" t="n">
+        <v>45665</v>
+      </c>
+      <c r="B508" t="n">
+        <v>0.06442101088376605</v>
+      </c>
+      <c r="C508" t="n">
+        <v>0.07314607277096534</v>
+      </c>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>Fold4</t>
+        </is>
+      </c>
+      <c r="E508" t="n">
+        <v>0.05580248142881271</v>
+      </c>
+      <c r="F508" t="n">
+        <v>0.0589085670806249</v>
+      </c>
+      <c r="G508" t="n">
+        <v>0.04889183913533365</v>
+      </c>
+      <c r="H508" t="n">
+        <v>0.04872575204129023</v>
+      </c>
+      <c r="I508" t="n">
+        <v>0.04284991580872215</v>
+      </c>
+      <c r="J508" t="n">
+        <v>0.04138751065555435</v>
+      </c>
+      <c r="K508" t="n">
+        <v>0.03804492672322611</v>
+      </c>
+      <c r="L508" t="n">
+        <v>0.03435914719800975</v>
+      </c>
+      <c r="M508" t="n">
+        <v>0.03279984026700371</v>
+      </c>
+      <c r="N508" t="n">
+        <v>0.02822514494943126</v>
+      </c>
+      <c r="O508" t="n">
+        <v>589.49</v>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" s="2" t="n">
+        <v>45667</v>
+      </c>
+      <c r="B509" t="n">
+        <v>-0.02073989471076766</v>
+      </c>
+      <c r="C509" t="n">
+        <v>-0.04273287425223306</v>
+      </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>Fold4</t>
+        </is>
+      </c>
+      <c r="E509" t="n">
+        <v>-0.01248309558782479</v>
+      </c>
+      <c r="F509" t="n">
+        <v>-0.030277248007049</v>
+      </c>
+      <c r="G509" t="n">
+        <v>-0.005749062460683018</v>
+      </c>
+      <c r="H509" t="n">
+        <v>-0.02155487424959739</v>
+      </c>
+      <c r="I509" t="n">
+        <v>-0.002980536379781949</v>
+      </c>
+      <c r="J509" t="n">
+        <v>-0.01843652028152265</v>
+      </c>
+      <c r="K509" t="n">
+        <v>-0.0009734794060674531</v>
+      </c>
+      <c r="L509" t="n">
+        <v>-0.01644451296435986</v>
+      </c>
+      <c r="M509" t="n">
+        <v>0.0006087899409067531</v>
+      </c>
+      <c r="N509" t="n">
+        <v>-0.01456339636087339</v>
+      </c>
+      <c r="O509" t="n">
+        <v>580.49</v>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" s="2" t="n">
+        <v>45670</v>
+      </c>
+      <c r="B510" t="n">
+        <v>-0.01938296667676885</v>
+      </c>
+      <c r="C510" t="n">
+        <v>-0.01750954278060045</v>
+      </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>Fold4</t>
+        </is>
+      </c>
+      <c r="E510" t="n">
+        <v>-0.01702337229920832</v>
+      </c>
+      <c r="F510" t="n">
+        <v>-0.01281028785624315</v>
+      </c>
+      <c r="G510" t="n">
+        <v>-0.0137045020208045</v>
+      </c>
+      <c r="H510" t="n">
+        <v>-0.008525158463010865</v>
+      </c>
+      <c r="I510" t="n">
+        <v>-0.01291993057574917</v>
+      </c>
+      <c r="J510" t="n">
+        <v>-0.00762809463161958</v>
+      </c>
+      <c r="K510" t="n">
+        <v>-0.01368478528588593</v>
+      </c>
+      <c r="L510" t="n">
+        <v>-0.006779943657105672</v>
+      </c>
+      <c r="M510" t="n">
+        <v>-0.01303349114856558</v>
+      </c>
+      <c r="N510" t="n">
+        <v>-0.005926162069167505</v>
+      </c>
+      <c r="O510" t="n">
+        <v>581.39</v>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" s="2" t="n">
+        <v>45671</v>
+      </c>
+      <c r="B511" t="n">
+        <v>-0.09069905593626008</v>
+      </c>
+      <c r="C511" t="n">
+        <v>-0.118042718172369</v>
+      </c>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>Fold4</t>
+        </is>
+      </c>
+      <c r="E511" t="n">
+        <v>-0.0662302421007684</v>
+      </c>
+      <c r="F511" t="n">
+        <v>-0.08402738923358913</v>
+      </c>
+      <c r="G511" t="n">
+        <v>-0.05291017844865943</v>
+      </c>
+      <c r="H511" t="n">
+        <v>-0.06517065687249546</v>
+      </c>
+      <c r="I511" t="n">
+        <v>-0.03960647092672206</v>
+      </c>
+      <c r="J511" t="n">
+        <v>-0.04935040800461438</v>
+      </c>
+      <c r="K511" t="n">
+        <v>-0.03286389177445612</v>
+      </c>
+      <c r="L511" t="n">
+        <v>-0.04206328746019657</v>
+      </c>
+      <c r="M511" t="n">
+        <v>-0.02794415298977686</v>
+      </c>
+      <c r="N511" t="n">
+        <v>-0.03635157519778742</v>
+      </c>
+      <c r="O511" t="n">
+        <v>582.1900000000001</v>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" s="2" t="n">
+        <v>45672</v>
+      </c>
+      <c r="B512" t="n">
+        <v>0.00257740853598042</v>
+      </c>
+      <c r="C512" t="n">
+        <v>0.01654679406451912</v>
+      </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>Fold4</t>
+        </is>
+      </c>
+      <c r="E512" t="n">
+        <v>-0.00199288322185229</v>
+      </c>
+      <c r="F512" t="n">
+        <v>0.01077219757825008</v>
+      </c>
+      <c r="G512" t="n">
+        <v>-0.003935112922193965</v>
+      </c>
+      <c r="H512" t="n">
+        <v>0.007897538720414734</v>
+      </c>
+      <c r="I512" t="n">
+        <v>-0.005658033780607712</v>
+      </c>
+      <c r="J512" t="n">
+        <v>0.005831361227987837</v>
+      </c>
+      <c r="K512" t="n">
+        <v>-0.006965279150606066</v>
+      </c>
+      <c r="L512" t="n">
+        <v>0.004985236639669387</v>
+      </c>
+      <c r="M512" t="n">
+        <v>-0.007382669784990015</v>
+      </c>
+      <c r="N512" t="n">
+        <v>0.004445794290708251</v>
+      </c>
+      <c r="O512" t="n">
+        <v>592.78</v>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" s="2" t="n">
+        <v>45673</v>
+      </c>
+      <c r="B513" t="n">
+        <v>0.007319780250740184</v>
+      </c>
+      <c r="C513" t="n">
+        <v>0.0106445218258869</v>
+      </c>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>Fold4</t>
+        </is>
+      </c>
+      <c r="E513" t="n">
+        <v>0.004832987374600276</v>
+      </c>
+      <c r="F513" t="n">
+        <v>0.00731554298309413</v>
+      </c>
+      <c r="G513" t="n">
+        <v>0.003928937776537618</v>
+      </c>
+      <c r="H513" t="n">
+        <v>0.005680595366497888</v>
+      </c>
+      <c r="I513" t="n">
+        <v>0.0007928672065900691</v>
+      </c>
+      <c r="J513" t="n">
+        <v>0.001868086308384336</v>
+      </c>
+      <c r="K513" t="n">
+        <v>0.003125419362452315</v>
+      </c>
+      <c r="L513" t="n">
+        <v>0.001517261833520301</v>
+      </c>
+      <c r="M513" t="n">
+        <v>0.003218198179290433</v>
+      </c>
+      <c r="N513" t="n">
+        <v>0.001595147972131559</v>
+      </c>
+      <c r="O513" t="n">
+        <v>591.64</v>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" s="2" t="n">
+        <v>45674</v>
+      </c>
+      <c r="B514" t="n">
+        <v>-0.04231357633841647</v>
+      </c>
+      <c r="C514" t="n">
+        <v>-0.07242825355045382</v>
+      </c>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>Fold4</t>
+        </is>
+      </c>
+      <c r="E514" t="n">
+        <v>-0.02585607985366955</v>
+      </c>
+      <c r="F514" t="n">
+        <v>-0.05028592323784593</v>
+      </c>
+      <c r="G514" t="n">
+        <v>-0.01748567462884988</v>
+      </c>
+      <c r="H514" t="n">
+        <v>-0.03867633471876383</v>
+      </c>
+      <c r="I514" t="n">
+        <v>-0.01124781262526478</v>
+      </c>
+      <c r="J514" t="n">
+        <v>-0.03131464696964559</v>
+      </c>
+      <c r="K514" t="n">
+        <v>-0.01085730996616579</v>
+      </c>
+      <c r="L514" t="n">
+        <v>-0.02706814968321598</v>
+      </c>
+      <c r="M514" t="n">
+        <v>-0.007658690881103321</v>
+      </c>
+      <c r="N514" t="n">
+        <v>-0.02337049660691018</v>
+      </c>
+      <c r="O514" t="n">
+        <v>597.58</v>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" s="2" t="n">
+        <v>45678</v>
+      </c>
+      <c r="B515" t="n">
+        <v>0.01241002075145357</v>
+      </c>
+      <c r="C515" t="n">
+        <v>0.03544139979398174</v>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>Fold4</t>
+        </is>
+      </c>
+      <c r="E515" t="n">
+        <v>0.01121452986072151</v>
+      </c>
+      <c r="F515" t="n">
+        <v>0.0299528051135561</v>
+      </c>
+      <c r="G515" t="n">
+        <v>0.006133278217073524</v>
+      </c>
+      <c r="H515" t="n">
+        <v>0.02275540526331611</v>
+      </c>
+      <c r="I515" t="n">
+        <v>0.002757977394073562</v>
+      </c>
+      <c r="J515" t="n">
+        <v>0.01877856549933522</v>
+      </c>
+      <c r="K515" t="n">
+        <v>0.003119816669227465</v>
+      </c>
+      <c r="L515" t="n">
+        <v>0.0163106300294988</v>
+      </c>
+      <c r="M515" t="n">
+        <v>0.001323184781016291</v>
+      </c>
+      <c r="N515" t="n">
+        <v>0.01423319784022667</v>
+      </c>
+      <c r="O515" t="n">
+        <v>603.05</v>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" s="2" t="n">
+        <v>45679</v>
+      </c>
+      <c r="B516" t="n">
+        <v>-0.01612471596462689</v>
+      </c>
+      <c r="C516" t="n">
+        <v>-0.02348738222533143</v>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>Fold4</t>
+        </is>
+      </c>
+      <c r="E516" t="n">
+        <v>-0.01376434364885786</v>
+      </c>
+      <c r="F516" t="n">
+        <v>-0.01853276587666136</v>
+      </c>
+      <c r="G516" t="n">
+        <v>-0.01007487721008895</v>
+      </c>
+      <c r="H516" t="n">
+        <v>-0.01382392751892275</v>
+      </c>
+      <c r="I516" t="n">
+        <v>-0.01000382919171609</v>
+      </c>
+      <c r="J516" t="n">
+        <v>-0.01391038981881847</v>
+      </c>
+      <c r="K516" t="n">
+        <v>-0.008434249019736745</v>
+      </c>
+      <c r="L516" t="n">
+        <v>-0.01234999987366699</v>
+      </c>
+      <c r="M516" t="n">
+        <v>-0.006880898744575923</v>
+      </c>
+      <c r="N516" t="n">
+        <v>-0.01057150868124855</v>
+      </c>
+      <c r="O516" t="n">
+        <v>606.4400000000001</v>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" s="2" t="n">
+        <v>45680</v>
+      </c>
+      <c r="B517" t="n">
+        <v>-0.005229258776488472</v>
+      </c>
+      <c r="C517" t="n">
+        <v>-0.008483482858977225</v>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>Fold4</t>
+        </is>
+      </c>
+      <c r="E517" t="n">
+        <v>-0.002410079676708532</v>
+      </c>
+      <c r="F517" t="n">
+        <v>-0.004452296430056547</v>
+      </c>
+      <c r="G517" t="n">
+        <v>-0.0005932134038241354</v>
+      </c>
+      <c r="H517" t="n">
+        <v>-0.002170844593729527</v>
+      </c>
+      <c r="I517" t="n">
+        <v>0.001906180860750268</v>
+      </c>
+      <c r="J517" t="n">
+        <v>0.0006218954505375949</v>
+      </c>
+      <c r="K517" t="n">
+        <v>0.001163956882985695</v>
+      </c>
+      <c r="L517" t="n">
+        <v>-0.0001458961393577005</v>
+      </c>
+      <c r="M517" t="n">
+        <v>0.0005311276880181336</v>
+      </c>
+      <c r="N517" t="n">
+        <v>-0.00105863704518206</v>
+      </c>
+      <c r="O517" t="n">
+        <v>609.75</v>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" s="2" t="n">
+        <v>45681</v>
+      </c>
+      <c r="B518" t="n">
+        <v>0.06744374649650786</v>
+      </c>
+      <c r="C518" t="n">
+        <v>0.08062950368535628</v>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>Fold4</t>
+        </is>
+      </c>
+      <c r="E518" t="n">
+        <v>0.03999099710002465</v>
+      </c>
+      <c r="F518" t="n">
+        <v>0.04801689682272918</v>
+      </c>
+      <c r="G518" t="n">
+        <v>0.03004065413067822</v>
+      </c>
+      <c r="H518" t="n">
+        <v>0.03438897281360799</v>
+      </c>
+      <c r="I518" t="n">
+        <v>0.02348880587072804</v>
+      </c>
+      <c r="J518" t="n">
+        <v>0.02683143025462969</v>
+      </c>
+      <c r="K518" t="n">
+        <v>0.02112652875402384</v>
+      </c>
+      <c r="L518" t="n">
+        <v>0.02421710545159362</v>
+      </c>
+      <c r="M518" t="n">
+        <v>0.01926104590375074</v>
+      </c>
+      <c r="N518" t="n">
+        <v>0.0222576579211258</v>
+      </c>
+      <c r="O518" t="n">
+        <v>607.97</v>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" s="2" t="n">
+        <v>45684</v>
+      </c>
+      <c r="B519" t="n">
+        <v>-0.03736195076811104</v>
+      </c>
+      <c r="C519" t="n">
+        <v>-0.02451797787723605</v>
+      </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>Fold4</t>
+        </is>
+      </c>
+      <c r="E519" t="n">
+        <v>-0.03067506364132242</v>
+      </c>
+      <c r="F519" t="n">
+        <v>-0.01570685114080214</v>
+      </c>
+      <c r="G519" t="n">
+        <v>-0.02761952863838821</v>
+      </c>
+      <c r="H519" t="n">
+        <v>-0.0114586606719979</v>
+      </c>
+      <c r="I519" t="n">
+        <v>-0.02344051885268342</v>
+      </c>
+      <c r="J519" t="n">
+        <v>-0.006556356202565098</v>
+      </c>
+      <c r="K519" t="n">
+        <v>-0.02274006543789229</v>
+      </c>
+      <c r="L519" t="n">
+        <v>-0.005815177866157873</v>
+      </c>
+      <c r="M519" t="n">
+        <v>-0.02243800920875156</v>
+      </c>
+      <c r="N519" t="n">
+        <v>-0.005553316070025961</v>
+      </c>
+      <c r="O519" t="n">
+        <v>599.37</v>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" s="2" t="n">
+        <v>45685</v>
+      </c>
+      <c r="B520" t="n">
+        <v>-0.003859233676456305</v>
+      </c>
+      <c r="C520" t="n">
+        <v>-0.01164149324155545</v>
+      </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>Fold4</t>
+        </is>
+      </c>
+      <c r="E520" t="n">
+        <v>0.0007965531396229227</v>
+      </c>
+      <c r="F520" t="n">
+        <v>-0.007057538009163637</v>
+      </c>
+      <c r="G520" t="n">
+        <v>0.0009567451256015194</v>
+      </c>
+      <c r="H520" t="n">
+        <v>-0.006775716418523725</v>
+      </c>
+      <c r="I520" t="n">
+        <v>0.001649411546216462</v>
+      </c>
+      <c r="J520" t="n">
+        <v>-0.005955913842151516</v>
+      </c>
+      <c r="K520" t="n">
+        <v>0.001620212585532321</v>
+      </c>
+      <c r="L520" t="n">
+        <v>-0.00483113038697889</v>
+      </c>
+      <c r="M520" t="n">
+        <v>0.002634631292113234</v>
+      </c>
+      <c r="N520" t="n">
+        <v>-0.003765105302825702</v>
+      </c>
+      <c r="O520" t="n">
+        <v>604.52</v>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" s="2" t="n">
+        <v>45686</v>
+      </c>
+      <c r="B521" t="n">
+        <v>-0.004941063544870495</v>
+      </c>
+      <c r="C521" t="n">
+        <v>-0.01628054488544572</v>
+      </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>Fold4</t>
+        </is>
+      </c>
+      <c r="E521" t="n">
+        <v>0.002024731330218152</v>
+      </c>
+      <c r="F521" t="n">
+        <v>-0.008999103981223177</v>
+      </c>
+      <c r="G521" t="n">
+        <v>0.003084299228524771</v>
+      </c>
+      <c r="H521" t="n">
+        <v>-0.007605342814218648</v>
+      </c>
+      <c r="I521" t="n">
+        <v>0.004422172143339005</v>
+      </c>
+      <c r="J521" t="n">
+        <v>-0.006112868748662979</v>
+      </c>
+      <c r="K521" t="n">
+        <v>0.006850965244959453</v>
+      </c>
+      <c r="L521" t="n">
+        <v>-0.005313565998588488</v>
+      </c>
+      <c r="M521" t="n">
+        <v>0.007616051278980892</v>
+      </c>
+      <c r="N521" t="n">
+        <v>-0.004589938545105796</v>
+      </c>
+      <c r="O521" t="n">
+        <v>601.8099999999999</v>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" s="2" t="n">
+        <v>45687</v>
+      </c>
+      <c r="B522" t="n">
+        <v>0.03357672336485632</v>
+      </c>
+      <c r="C522" t="n">
+        <v>0.02928662321467324</v>
+      </c>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>Fold4</t>
+        </is>
+      </c>
+      <c r="E522" t="n">
+        <v>0.02475780146635331</v>
+      </c>
+      <c r="F522" t="n">
+        <v>0.01870099907457911</v>
+      </c>
+      <c r="G522" t="n">
+        <v>0.02170221909467635</v>
+      </c>
+      <c r="H522" t="n">
+        <v>0.01425855150609851</v>
+      </c>
+      <c r="I522" t="n">
+        <v>0.01916556857957124</v>
+      </c>
+      <c r="J522" t="n">
+        <v>0.01122153712800013</v>
+      </c>
+      <c r="K522" t="n">
+        <v>0.01824163162486729</v>
+      </c>
+      <c r="L522" t="n">
+        <v>0.009636967032816988</v>
+      </c>
+      <c r="M522" t="n">
+        <v>0.01719841298931159</v>
+      </c>
+      <c r="N522" t="n">
+        <v>0.008438326771409353</v>
+      </c>
+      <c r="O522" t="n">
+        <v>605.04</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
